--- a/ig/nr-add-doc/ValueSet-MeltingPotVS.xlsx
+++ b/ig/nr-add-doc/ValueSet-MeltingPotVS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T10:24:04+00:00</t>
+    <t>2023-05-04T12:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-doc/ValueSet-MeltingPotVS.xlsx
+++ b/ig/nr-add-doc/ValueSet-MeltingPotVS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:01:17+00:00</t>
+    <t>2023-05-04T12:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-doc/ValueSet-MeltingPotVS.xlsx
+++ b/ig/nr-add-doc/ValueSet-MeltingPotVS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:02:02+00:00</t>
+    <t>2023-05-04T12:22:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-doc/ValueSet-MeltingPotVS.xlsx
+++ b/ig/nr-add-doc/ValueSet-MeltingPotVS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:22:59+00:00</t>
+    <t>2023-05-05T12:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
